--- a/week-01/techsupply_dataset.xlsx
+++ b/week-01/techsupply_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\disco\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE5D617-CA9B-4541-95D5-7BC6E33C3BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9314AC-1F22-4C85-93F1-BCD56AF3D41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales_Data" sheetId="1" r:id="rId1"/>
